--- a/public/templates/CLRA_Act_1970/CLRA Form XIV-XVI Muster Roll.xlsx
+++ b/public/templates/CLRA_Act_1970/CLRA Form XIV-XVI Muster Roll.xlsx
@@ -378,7 +378,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -406,29 +406,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFB3B3"/>
-        <bgColor rgb="FFFF99CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -441,21 +423,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -484,60 +451,68 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -570,7 +545,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -586,12 +561,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFD9EAD3"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFB3B3"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -599,7 +574,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFC55A11"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FFA0A0A0"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -796,822 +771,822 @@
   <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="6" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="37" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="6" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="37" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="3"/>
-      <c r="AQ3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
+      <c r="AL3" s="4"/>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="S4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="T4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="U4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="V4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="Z4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AA4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AB4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AC4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AD4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AE4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AF4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AG4" s="5" t="s">
+      <c r="AG4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AH4" s="5" t="s">
+      <c r="AH4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AI4" s="5" t="s">
+      <c r="AI4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AJ4" s="5" t="s">
+      <c r="AJ4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AK4" s="5" t="s">
+      <c r="AK4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AL4" s="5" t="s">
+      <c r="AL4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AM4" s="5" t="s">
+      <c r="AM4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AN4" s="5" t="s">
+      <c r="AN4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AO4" s="5" t="s">
+      <c r="AO4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AP4" s="5" t="s">
+      <c r="AP4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AQ4" s="5" t="s">
+      <c r="AQ4" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="P5" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q5" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="R5" s="9" t="s">
+      <c r="R5" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="S5" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="T5" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="U5" s="9" t="s">
+      <c r="U5" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="V5" s="9" t="s">
+      <c r="V5" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="W5" s="9" t="s">
+      <c r="W5" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="X5" s="9" t="s">
+      <c r="X5" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="Y5" s="9" t="s">
+      <c r="Y5" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="Z5" s="9" t="s">
+      <c r="Z5" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AA5" s="9" t="s">
+      <c r="AA5" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AB5" s="9" t="s">
+      <c r="AB5" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AC5" s="9" t="s">
+      <c r="AC5" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="AD5" s="9" t="s">
+      <c r="AD5" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="AE5" s="9" t="s">
+      <c r="AE5" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AF5" s="9" t="s">
+      <c r="AF5" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="AG5" s="9" t="s">
+      <c r="AG5" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="AH5" s="9" t="s">
+      <c r="AH5" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AI5" s="9" t="s">
+      <c r="AI5" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AJ5" s="9" t="s">
+      <c r="AJ5" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="AK5" s="7" t="s">
+      <c r="AK5" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="AL5" s="7" t="s">
+      <c r="AL5" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="AM5" s="9" t="s">
+      <c r="AM5" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="AN5" s="10" t="s">
+      <c r="AN5" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AO5" s="10" t="s">
+      <c r="AO5" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="AP5" s="9" t="s">
+      <c r="AP5" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="AQ5" s="9" t="s">
+      <c r="AQ5" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="11"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="12"/>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="12"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="11"/>
-      <c r="AK6" s="11"/>
-      <c r="AL6" s="11"/>
-      <c r="AM6" s="11"/>
-      <c r="AN6" s="11"/>
-      <c r="AO6" s="11"/>
-      <c r="AP6" s="11"/>
-      <c r="AQ6" s="11"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="15"/>
+      <c r="AF6" s="15"/>
+      <c r="AG6" s="15"/>
+      <c r="AH6" s="15"/>
+      <c r="AI6" s="15"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="14"/>
+      <c r="AL6" s="14"/>
+      <c r="AM6" s="14"/>
+      <c r="AN6" s="14"/>
+      <c r="AO6" s="14"/>
+      <c r="AP6" s="14"/>
+      <c r="AQ6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="11"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="11"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="12"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="13"/>
-      <c r="AI7" s="13"/>
-      <c r="AJ7" s="11"/>
-      <c r="AK7" s="11"/>
-      <c r="AL7" s="11"/>
-      <c r="AM7" s="11"/>
-      <c r="AN7" s="11"/>
-      <c r="AO7" s="11"/>
-      <c r="AP7" s="11"/>
-      <c r="AQ7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="15"/>
+      <c r="AF7" s="15"/>
+      <c r="AG7" s="15"/>
+      <c r="AH7" s="15"/>
+      <c r="AI7" s="15"/>
+      <c r="AJ7" s="14"/>
+      <c r="AK7" s="14"/>
+      <c r="AL7" s="14"/>
+      <c r="AM7" s="14"/>
+      <c r="AN7" s="14"/>
+      <c r="AO7" s="14"/>
+      <c r="AP7" s="14"/>
+      <c r="AQ7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="11"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="11"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="13"/>
-      <c r="AI8" s="13"/>
-      <c r="AJ8" s="11"/>
-      <c r="AK8" s="11"/>
-      <c r="AL8" s="11"/>
-      <c r="AM8" s="11"/>
-      <c r="AN8" s="11"/>
-      <c r="AO8" s="11"/>
-      <c r="AP8" s="11"/>
-      <c r="AQ8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="15"/>
+      <c r="AF8" s="15"/>
+      <c r="AG8" s="15"/>
+      <c r="AH8" s="15"/>
+      <c r="AI8" s="15"/>
+      <c r="AJ8" s="14"/>
+      <c r="AK8" s="14"/>
+      <c r="AL8" s="14"/>
+      <c r="AM8" s="14"/>
+      <c r="AN8" s="14"/>
+      <c r="AO8" s="14"/>
+      <c r="AP8" s="14"/>
+      <c r="AQ8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="11"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="11"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="12"/>
-      <c r="AF9" s="12"/>
-      <c r="AG9" s="12"/>
-      <c r="AH9" s="13"/>
-      <c r="AI9" s="13"/>
-      <c r="AJ9" s="11"/>
-      <c r="AK9" s="11"/>
-      <c r="AL9" s="11"/>
-      <c r="AM9" s="11"/>
-      <c r="AN9" s="11"/>
-      <c r="AO9" s="11"/>
-      <c r="AP9" s="11"/>
-      <c r="AQ9" s="11"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="15"/>
+      <c r="AG9" s="15"/>
+      <c r="AH9" s="15"/>
+      <c r="AI9" s="15"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="11"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="12"/>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="13"/>
-      <c r="AI10" s="13"/>
-      <c r="AJ10" s="11"/>
-      <c r="AK10" s="11"/>
-      <c r="AL10" s="11"/>
-      <c r="AM10" s="11"/>
-      <c r="AN10" s="11"/>
-      <c r="AO10" s="11"/>
-      <c r="AP10" s="11"/>
-      <c r="AQ10" s="11"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="14"/>
+      <c r="AK10" s="14"/>
+      <c r="AL10" s="14"/>
+      <c r="AM10" s="14"/>
+      <c r="AN10" s="14"/>
+      <c r="AO10" s="14"/>
+      <c r="AP10" s="14"/>
+      <c r="AQ10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="11"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="11"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="12"/>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AH11" s="13"/>
-      <c r="AI11" s="13"/>
-      <c r="AJ11" s="11"/>
-      <c r="AK11" s="11"/>
-      <c r="AL11" s="11"/>
-      <c r="AM11" s="11"/>
-      <c r="AN11" s="11"/>
-      <c r="AO11" s="11"/>
-      <c r="AP11" s="11"/>
-      <c r="AQ11" s="11"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="15"/>
+      <c r="AF11" s="15"/>
+      <c r="AG11" s="15"/>
+      <c r="AH11" s="15"/>
+      <c r="AI11" s="15"/>
+      <c r="AJ11" s="14"/>
+      <c r="AK11" s="14"/>
+      <c r="AL11" s="14"/>
+      <c r="AM11" s="14"/>
+      <c r="AN11" s="14"/>
+      <c r="AO11" s="14"/>
+      <c r="AP11" s="14"/>
+      <c r="AQ11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="12"/>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="11"/>
-      <c r="AK12" s="11"/>
-      <c r="AL12" s="11"/>
-      <c r="AM12" s="11"/>
-      <c r="AN12" s="11"/>
-      <c r="AO12" s="11"/>
-      <c r="AP12" s="11"/>
-      <c r="AQ12" s="11"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="15"/>
+      <c r="AF12" s="15"/>
+      <c r="AG12" s="15"/>
+      <c r="AH12" s="15"/>
+      <c r="AI12" s="15"/>
+      <c r="AJ12" s="14"/>
+      <c r="AK12" s="14"/>
+      <c r="AL12" s="14"/>
+      <c r="AM12" s="14"/>
+      <c r="AN12" s="14"/>
+      <c r="AO12" s="14"/>
+      <c r="AP12" s="14"/>
+      <c r="AQ12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="11"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="12"/>
-      <c r="AF13" s="12"/>
-      <c r="AG13" s="12"/>
-      <c r="AH13" s="13"/>
-      <c r="AI13" s="13"/>
-      <c r="AJ13" s="11"/>
-      <c r="AK13" s="11"/>
-      <c r="AL13" s="11"/>
-      <c r="AM13" s="11"/>
-      <c r="AN13" s="11"/>
-      <c r="AO13" s="11"/>
-      <c r="AP13" s="11"/>
-      <c r="AQ13" s="11"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="15"/>
+      <c r="AF13" s="15"/>
+      <c r="AG13" s="15"/>
+      <c r="AH13" s="15"/>
+      <c r="AI13" s="15"/>
+      <c r="AJ13" s="14"/>
+      <c r="AK13" s="14"/>
+      <c r="AL13" s="14"/>
+      <c r="AM13" s="14"/>
+      <c r="AN13" s="14"/>
+      <c r="AO13" s="14"/>
+      <c r="AP13" s="14"/>
+      <c r="AQ13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="11"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="12"/>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="12"/>
-      <c r="AH14" s="13"/>
-      <c r="AI14" s="13"/>
-      <c r="AJ14" s="11"/>
-      <c r="AK14" s="11"/>
-      <c r="AL14" s="11"/>
-      <c r="AM14" s="11"/>
-      <c r="AN14" s="11"/>
-      <c r="AO14" s="11"/>
-      <c r="AP14" s="11"/>
-      <c r="AQ14" s="11"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14"/>
+      <c r="AA14" s="14"/>
+      <c r="AB14" s="14"/>
+      <c r="AC14" s="14"/>
+      <c r="AD14" s="14"/>
+      <c r="AE14" s="15"/>
+      <c r="AF14" s="15"/>
+      <c r="AG14" s="15"/>
+      <c r="AH14" s="15"/>
+      <c r="AI14" s="15"/>
+      <c r="AJ14" s="14"/>
+      <c r="AK14" s="14"/>
+      <c r="AL14" s="14"/>
+      <c r="AM14" s="14"/>
+      <c r="AN14" s="14"/>
+      <c r="AO14" s="14"/>
+      <c r="AP14" s="14"/>
+      <c r="AQ14" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="3">
